--- a/evaluation_forms/020_health_professions_scholarship_evaluation--evaluation_forms.xlsx
+++ b/evaluation_forms/020_health_professions_scholarship_evaluation--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'interpersonal_skills'}</t>
+          <t>interpersonal_skills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Interpersonal Skills'}</t>
+          <t>Interpersonal Skills</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'professionalism'}</t>
+          <t>professionalism</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Professionalism'}</t>
+          <t>Professionalism</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'1_-_excellent'}</t>
+          <t>1_-_excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '1 - Excellent'}</t>
+          <t>1 - Excellent</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'2_-_good'}</t>
+          <t>2_-_good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '2 - Good'}</t>
+          <t>2 - Good</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'3_-_fair'}</t>
+          <t>3_-_fair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '3 - Fair'}</t>
+          <t>3 - Fair</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'4_-_needs_improvement'}</t>
+          <t>4_-_needs_improvement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '4 - Needs Improvement'}</t>
+          <t>4 - Needs Improvement</t>
         </is>
       </c>
     </row>
